--- a/tests/ITER_3D_APEC_evol_fine2/input_template.xlsx
+++ b/tests/ITER_3D_APEC_evol_fine2/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>

--- a/tests/ITER_3D_APEC_evol_fine2/input_template.xlsx
+++ b/tests/ITER_3D_APEC_evol_fine2/input_template.xlsx
@@ -695,22 +695,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
@@ -727,22 +727,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
@@ -768,13 +768,13 @@
         <v>8e-07</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
